--- a/表格模版/德邦空派.xlsx
+++ b/表格模版/德邦空派.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27600" windowHeight="13480"/>
+    <workbookView windowWidth="27860" windowHeight="9520"/>
   </bookViews>
   <sheets>
     <sheet name="箱单发票" sheetId="1" r:id="rId1"/>
@@ -16,12 +16,8 @@
 </workbook>
 </file>
 
-<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>单号 Courier number</t>
   </si>
@@ -36,12 +32,6 @@
   </si>
   <si>
     <t>地址 ADRESS：</t>
-  </si>
-  <si>
-    <t>TMB8，
-27505 SW 132nd AVE，
-United States of America (USA)，
-HOMESTEAD，FL，33032-8597</t>
   </si>
   <si>
     <t>收件人姓名：（私人地址需填写）:</t>
@@ -1579,9 +1569,7 @@
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
       <c r="K5" s="21"/>
-      <c r="L5" s="25" t="s">
-        <v>5</v>
-      </c>
+      <c r="L5" s="25"/>
       <c r="M5" s="11"/>
       <c r="N5" s="11"/>
       <c r="O5" s="11"/>
@@ -1591,7 +1579,7 @@
     </row>
     <row r="6" ht="48.75" customHeight="1" spans="2:18">
       <c r="B6" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="11"/>
@@ -1599,7 +1587,7 @@
       <c r="F6" s="11"/>
       <c r="G6" s="21"/>
       <c r="H6" s="10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
@@ -1614,51 +1602,51 @@
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="2:18">
       <c r="B7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="D7" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="F7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="G7" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="H7" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="I7" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="J7" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="22" t="s">
+      <c r="K7" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="L7" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>18</v>
       </c>
       <c r="M7" s="11"/>
       <c r="N7" s="21"/>
       <c r="O7" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="P7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="Q7" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="Q7" s="31" t="s">
+      <c r="R7" s="32" t="s">
         <v>21</v>
-      </c>
-      <c r="R7" s="32" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" spans="2:18">
@@ -1673,13 +1661,13 @@
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
       <c r="L8" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="M8" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="N8" s="23" t="s">
         <v>24</v>
-      </c>
-      <c r="N8" s="23" t="s">
-        <v>25</v>
       </c>
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
@@ -1707,7 +1695,7 @@
     </row>
     <row r="10" ht="36" customHeight="1" spans="2:18">
       <c r="B10" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>

--- a/表格模版/德邦空派.xlsx
+++ b/表格模版/德邦空派.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27860" windowHeight="9520"/>
+    <workbookView windowWidth="23660" windowHeight="7940"/>
   </bookViews>
   <sheets>
     <sheet name="箱单发票" sheetId="1" r:id="rId1"/>
@@ -17,15 +17,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>单号 Courier number</t>
   </si>
   <si>
     <t>日期  Date:</t>
-  </si>
-  <si>
-    <t>2024.12.02</t>
   </si>
   <si>
     <t>公司名  COMPANY:</t>
@@ -1544,9 +1541,7 @@
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
       <c r="K4" s="20"/>
-      <c r="L4" s="24" t="s">
-        <v>2</v>
-      </c>
+      <c r="L4" s="24"/>
       <c r="M4" s="20"/>
       <c r="N4" s="27"/>
       <c r="O4" s="27"/>
@@ -1556,7 +1551,7 @@
     </row>
     <row r="5" ht="97" customHeight="1" spans="2:18">
       <c r="B5" s="9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="11"/>
@@ -1564,7 +1559,7 @@
       <c r="F5" s="11"/>
       <c r="G5" s="21"/>
       <c r="H5" s="10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" s="11"/>
       <c r="J5" s="11"/>
@@ -1579,7 +1574,7 @@
     </row>
     <row r="6" ht="48.75" customHeight="1" spans="2:18">
       <c r="B6" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="11"/>
@@ -1587,7 +1582,7 @@
       <c r="F6" s="11"/>
       <c r="G6" s="21"/>
       <c r="H6" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
@@ -1602,51 +1597,51 @@
     </row>
     <row r="7" ht="27.95" customHeight="1" spans="2:18">
       <c r="B7" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="D7" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="E7" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="F7" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="G7" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="H7" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="I7" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="22" t="s">
+      <c r="J7" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="J7" s="22" t="s">
+      <c r="K7" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="L7" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>17</v>
       </c>
       <c r="M7" s="11"/>
       <c r="N7" s="21"/>
       <c r="O7" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="P7" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="Q7" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="Q7" s="31" t="s">
+      <c r="R7" s="32" t="s">
         <v>20</v>
-      </c>
-      <c r="R7" s="32" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="8" ht="60" customHeight="1" spans="2:18">
@@ -1661,13 +1656,13 @@
       <c r="J8" s="15"/>
       <c r="K8" s="15"/>
       <c r="L8" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M8" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="N8" s="23" t="s">
         <v>23</v>
-      </c>
-      <c r="N8" s="23" t="s">
-        <v>24</v>
       </c>
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
@@ -1695,7 +1690,7 @@
     </row>
     <row r="10" ht="36" customHeight="1" spans="2:18">
       <c r="B10" s="18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
